--- a/Data/Clientes.xlsx
+++ b/Data/Clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\-Auditoria\Control_pagos_anticipos_CyA\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80613C77-E201-4AE3-ADF5-C8CADA7E29A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7160675F-38BD-4F87-A5DB-D98EACD62012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3090" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
   <si>
     <t>Cliente</t>
   </si>
@@ -40,25 +40,232 @@
     <t>Error</t>
   </si>
   <si>
+    <t>AGRICOLA GANADERA SAN JOSE SA</t>
+  </si>
+  <si>
+    <t>Imperio2025</t>
+  </si>
+  <si>
     <t>C:\Proyectos\-Auditoria\Control_pagos_anticipos_CyA\Data\Anticipos</t>
   </si>
   <si>
+    <t>AGRO BARGE SA</t>
+  </si>
+  <si>
+    <t>Santiago2025</t>
+  </si>
+  <si>
+    <t>AGROFRANCA SA</t>
+  </si>
+  <si>
+    <t>AGROSERVICIOS LA REVANCHA SA</t>
+  </si>
+  <si>
+    <t>Revancha2025</t>
+  </si>
+  <si>
+    <t>AGUAS &amp; PROCESOS SA</t>
+  </si>
+  <si>
+    <t>x4_6+aG3wwM6</t>
+  </si>
+  <si>
+    <t>BRACCO Y PORTA SA</t>
+  </si>
+  <si>
+    <t>OBracco63635</t>
+  </si>
+  <si>
+    <t>CDIMEX SA</t>
+  </si>
+  <si>
+    <t>Rafaela887</t>
+  </si>
+  <si>
+    <t>CONECTAR SRL</t>
+  </si>
+  <si>
+    <t>Crippa2025</t>
+  </si>
+  <si>
+    <t>COOP AGROPECUARIA "LA ARGENTINA" LTDA</t>
+  </si>
+  <si>
+    <t>Losbiava2025</t>
+  </si>
+  <si>
+    <t>DELLASANTA COMERCIAL SA</t>
+  </si>
+  <si>
+    <t>Oscar55OscarDE25</t>
+  </si>
+  <si>
+    <t>DOS LEGADOS SA</t>
+  </si>
+  <si>
+    <t>2025Gstuber</t>
+  </si>
+  <si>
+    <t>ECOWATT SAS</t>
+  </si>
+  <si>
+    <t>8x8bUlGe6T.7</t>
+  </si>
+  <si>
+    <t>ELECTRICIDAD PAGLIAROLI SA</t>
+  </si>
+  <si>
+    <t>Ginopa2025</t>
+  </si>
+  <si>
+    <t>ELECTROINSUMOS SA</t>
+  </si>
+  <si>
+    <t>Estudio2025GB</t>
+  </si>
+  <si>
+    <t>EQUIPOS AGROINDUSTRIALES SA</t>
+  </si>
+  <si>
+    <t>Guillermot37</t>
+  </si>
+  <si>
+    <t>ESCOBAR LITORAL SA</t>
+  </si>
+  <si>
+    <t>ESTAB. CANTAMALA SA</t>
+  </si>
+  <si>
+    <t>LGisbert397+</t>
+  </si>
+  <si>
+    <t>ESTUDIO RIVAROSSA Y ASOCIADOS</t>
+  </si>
+  <si>
+    <t>Emilia2025</t>
+  </si>
+  <si>
+    <t>ETMA SA</t>
+  </si>
+  <si>
+    <t>ACAGRA724p</t>
+  </si>
+  <si>
+    <t>GRUPO INBIO SA</t>
+  </si>
+  <si>
+    <t>FMarco2024</t>
+  </si>
+  <si>
+    <t>HERMANOS FUX SRL</t>
+  </si>
+  <si>
+    <t>Clarabu2025</t>
+  </si>
+  <si>
+    <t>ISIDORO S DELLASANTA y CÍA SAI y C</t>
+  </si>
+  <si>
+    <t>JIT INDUSTRIAL SA</t>
+  </si>
+  <si>
+    <t>Turc2025diego</t>
+  </si>
+  <si>
+    <t>LCGI SA</t>
+  </si>
+  <si>
+    <t>PabloB2025</t>
+  </si>
+  <si>
+    <t>LOS NARANJOS SA</t>
+  </si>
+  <si>
+    <t>w8BrI!6#S4r2</t>
+  </si>
+  <si>
+    <t>LZT AGRO SA</t>
+  </si>
+  <si>
+    <t>Lztagro2025</t>
+  </si>
+  <si>
+    <t>METALURGICA SAPINO SA</t>
+  </si>
+  <si>
+    <t>Roberto2025</t>
+  </si>
+  <si>
+    <t>METALÚRGICA SARMIENTO SRL</t>
+  </si>
+  <si>
+    <t>VictorSar2025</t>
+  </si>
+  <si>
     <t>NATION MOTORS SA</t>
   </si>
   <si>
     <t>Estudio2025</t>
   </si>
   <si>
-    <t>PACKING BOX SA</t>
-  </si>
-  <si>
-    <t>((#Urquiza##7411))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SURGENTE MOLINOS SA </t>
+    <t>NATION SA</t>
+  </si>
+  <si>
+    <t>PLACE SA</t>
+  </si>
+  <si>
+    <t>ReneCh2023</t>
+  </si>
+  <si>
+    <t>ROBLE BIENES RAÍCES SA</t>
+  </si>
+  <si>
+    <t>EstudioR2025</t>
+  </si>
+  <si>
+    <t>SICEMI SCA</t>
+  </si>
+  <si>
+    <t>SURGENTE MOLINOS SA</t>
   </si>
   <si>
     <t>Mantovani2025</t>
+  </si>
+  <si>
+    <t>TECHNO SA</t>
+  </si>
+  <si>
+    <t>Contarde2025</t>
+  </si>
+  <si>
+    <t>TELCO INVERSORA SA</t>
+  </si>
+  <si>
+    <t>Carloswil25</t>
+  </si>
+  <si>
+    <t>TRANSPORTE LA 19 SA</t>
+  </si>
+  <si>
+    <t>TREVISO SA</t>
+  </si>
+  <si>
+    <t>Jctrinca25</t>
+  </si>
+  <si>
+    <t>TRON SA</t>
+  </si>
+  <si>
+    <t>656ADiaz98</t>
+  </si>
+  <si>
+    <t>WILSON SA</t>
+  </si>
+  <si>
+    <t>WILTEL COMUNICACIONES SA</t>
+  </si>
+  <si>
+    <t>eSTUDIO2026</t>
   </si>
 </sst>
 </file>
@@ -421,14 +628,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="1" max="1" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -453,19 +661,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>20295204681</v>
+      </c>
+      <c r="C2">
+        <v>30710314353</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>27305018487</v>
-      </c>
-      <c r="C2">
-        <v>30717391264</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -473,16 +681,16 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>20111155500</v>
+        <v>20062779137</v>
       </c>
       <c r="C3">
-        <v>30718452704</v>
+        <v>30711572410</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -490,16 +698,662 @@
         <v>11</v>
       </c>
       <c r="B4">
+        <v>20285770018</v>
+      </c>
+      <c r="C4">
+        <v>30718810651</v>
+      </c>
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>20329004385</v>
+      </c>
+      <c r="C5">
+        <v>33711615739</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>20248502704</v>
+      </c>
+      <c r="C6">
+        <v>33602289619</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>20106361747</v>
+      </c>
+      <c r="C7">
+        <v>30518800775</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>20146535349</v>
+      </c>
+      <c r="C8">
+        <v>30711314489</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>20301913053</v>
+      </c>
+      <c r="C9">
+        <v>30717751414</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>20278913520</v>
+      </c>
+      <c r="C10">
+        <v>30605694191</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>20163036550</v>
+      </c>
+      <c r="C11">
+        <v>30708924896</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>20307649226</v>
+      </c>
+      <c r="C12">
+        <v>30709634751</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>20282211018</v>
+      </c>
+      <c r="C13">
+        <v>30716468867</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>20935609403</v>
+      </c>
+      <c r="C14">
+        <v>30718725522</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>23313646009</v>
+      </c>
+      <c r="C15">
+        <v>33713343809</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>20165740700</v>
+      </c>
+      <c r="C16">
+        <v>30707213899</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>20295204681</v>
+      </c>
+      <c r="C17">
+        <v>30715417223</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <v>20173958863</v>
+      </c>
+      <c r="C18">
+        <v>30711726183</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19">
+        <v>20246845612</v>
+      </c>
+      <c r="C19">
+        <v>30715561227</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20">
+        <v>27143384107</v>
+      </c>
+      <c r="C20">
+        <v>30505523225</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21">
+        <v>20275663973</v>
+      </c>
+      <c r="C21">
+        <v>30711642575</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>27340827061</v>
+      </c>
+      <c r="C22">
+        <v>30716870789</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>20163036550</v>
+      </c>
+      <c r="C23">
+        <v>30501721049</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24">
+        <v>20161700860</v>
+      </c>
+      <c r="C24">
+        <v>30717882306</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25">
+        <v>20291157255</v>
+      </c>
+      <c r="C25">
+        <v>30715084011</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26">
+        <v>20062610337</v>
+      </c>
+      <c r="C26">
+        <v>30710847742</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <v>27146539705</v>
+      </c>
+      <c r="C27">
+        <v>33717433349</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28">
+        <v>20106363669</v>
+      </c>
+      <c r="C28">
+        <v>30714610291</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>23117583309</v>
+      </c>
+      <c r="C29">
+        <v>30687011941</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30">
+        <v>27305018487</v>
+      </c>
+      <c r="C30">
+        <v>30717391264</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31">
+        <v>23083223979</v>
+      </c>
+      <c r="C31">
+        <v>30581697488</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32">
+        <v>20113062437</v>
+      </c>
+      <c r="C32">
+        <v>30711603154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33">
+        <v>27123041696</v>
+      </c>
+      <c r="C33">
+        <v>30711669163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34">
+        <v>23083223979</v>
+      </c>
+      <c r="C34">
+        <v>30600549991</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35">
         <v>20171140723</v>
       </c>
-      <c r="C4">
+      <c r="C35">
         <v>30711767645</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36">
+        <v>20132420921</v>
+      </c>
+      <c r="C36">
+        <v>30718347803</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37">
+        <v>20169574597</v>
+      </c>
+      <c r="C37">
+        <v>30712789707</v>
+      </c>
+      <c r="D37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38">
+        <v>20173958863</v>
+      </c>
+      <c r="C38">
+        <v>33711709199</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39">
+        <v>23162006789</v>
+      </c>
+      <c r="C39">
+        <v>30708873965</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40">
+        <v>20131338245</v>
+      </c>
+      <c r="C40">
+        <v>30645578070</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41">
+        <v>20169574597</v>
+      </c>
+      <c r="C41">
+        <v>30684389374</v>
+      </c>
+      <c r="D41" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42">
+        <v>20169574597</v>
+      </c>
+      <c r="C42">
+        <v>30684386308</v>
+      </c>
+      <c r="D42" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Clientes.xlsx
+++ b/Data/Clientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\-Auditoria\Control_pagos_anticipos_CyA\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7160675F-38BD-4F87-A5DB-D98EACD62012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A7DCBD-6FF9-4BE7-8724-F8D7494EAE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3165" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="89">
   <si>
     <t>Cliente</t>
   </si>
@@ -40,232 +40,253 @@
     <t>Error</t>
   </si>
   <si>
+    <t>C:\Proyectos\-Auditoria\Control_pagos_anticipos_CyA\Data\Anticipos</t>
+  </si>
+  <si>
+    <t>AGRO BARGE SA</t>
+  </si>
+  <si>
+    <t>Santiago2026</t>
+  </si>
+  <si>
+    <t>AGROFRANCA SA</t>
+  </si>
+  <si>
+    <t>eSTUDIO2026</t>
+  </si>
+  <si>
+    <t>AGUAS &amp; PROCESOS SA</t>
+  </si>
+  <si>
+    <t>z8rD=6*M8z8H</t>
+  </si>
+  <si>
+    <t>BRACCO Y PORTA SA</t>
+  </si>
+  <si>
+    <t>OBracco63635</t>
+  </si>
+  <si>
+    <t>CDIMEX SA</t>
+  </si>
+  <si>
+    <t>Rafaela887</t>
+  </si>
+  <si>
+    <t>CONECTAR SRL</t>
+  </si>
+  <si>
+    <t>Crippa2025</t>
+  </si>
+  <si>
+    <t>COOP AGROPECUARIA LA ARGENTINA LTDA</t>
+  </si>
+  <si>
+    <t>Losbiava2026</t>
+  </si>
+  <si>
+    <t>DELLASANTA COMERCIAL SA</t>
+  </si>
+  <si>
+    <t>Oscar55OscarDE25</t>
+  </si>
+  <si>
+    <t>DOS LEGADOS SA</t>
+  </si>
+  <si>
+    <t>2025Gstuber</t>
+  </si>
+  <si>
+    <t>ECOWATT SAS</t>
+  </si>
+  <si>
+    <t>dFp:1=Jkdc39</t>
+  </si>
+  <si>
+    <t>ELECTRICIDAD PAGLIAROLI SA</t>
+  </si>
+  <si>
+    <t>Ginopa2026</t>
+  </si>
+  <si>
+    <t>ELECTROINSUMOS SA</t>
+  </si>
+  <si>
+    <t>Estudio2025GB</t>
+  </si>
+  <si>
+    <t>ESTAB. CANTAMALA SA</t>
+  </si>
+  <si>
+    <t>LGisbert397+</t>
+  </si>
+  <si>
+    <t>ETMA SA</t>
+  </si>
+  <si>
+    <t>ACAGRA724p</t>
+  </si>
+  <si>
+    <t>GRUPO INBIO SA</t>
+  </si>
+  <si>
+    <t>FMarco2026</t>
+  </si>
+  <si>
+    <t>HERMANOS FUX SRL</t>
+  </si>
+  <si>
+    <t>Clarabu2025</t>
+  </si>
+  <si>
+    <t>INTEGRAL SA</t>
+  </si>
+  <si>
+    <t>Jctrinca26</t>
+  </si>
+  <si>
+    <t>ISIDORO S DELLASANTA y CÍA SAI y C</t>
+  </si>
+  <si>
+    <t>JIT INDUSTRIAL SA</t>
+  </si>
+  <si>
+    <t>Estudio2026</t>
+  </si>
+  <si>
+    <t>LCGI SA</t>
+  </si>
+  <si>
+    <t>PabloB2025</t>
+  </si>
+  <si>
+    <t>LOS NARANJOS SA</t>
+  </si>
+  <si>
+    <t>xU=95ppT7y0c</t>
+  </si>
+  <si>
+    <t>LZT AGRO SA</t>
+  </si>
+  <si>
+    <t>Lztagro2025</t>
+  </si>
+  <si>
+    <t>METALURGICA SAPINO SA</t>
+  </si>
+  <si>
+    <t>Roberto2026</t>
+  </si>
+  <si>
+    <t>NATION MOTORS SA</t>
+  </si>
+  <si>
+    <t>Estudio2025</t>
+  </si>
+  <si>
+    <t>NATION SA</t>
+  </si>
+  <si>
+    <t>Imperio2025</t>
+  </si>
+  <si>
+    <t>PLACE SA</t>
+  </si>
+  <si>
+    <t>ReneCh2023</t>
+  </si>
+  <si>
+    <t>SEPROP SA</t>
+  </si>
+  <si>
+    <t>Marcelo2025</t>
+  </si>
+  <si>
+    <t>SERVICIOS Y AGROPECUARIA DON JULIO SA</t>
+  </si>
+  <si>
+    <t>Jacobe2025</t>
+  </si>
+  <si>
+    <t>SICEMI SCA</t>
+  </si>
+  <si>
+    <t>TRANSPORTE LA 19 SA</t>
+  </si>
+  <si>
+    <t>TRON SA</t>
+  </si>
+  <si>
     <t>AGRICOLA GANADERA SAN JOSE SA</t>
   </si>
   <si>
-    <t>Imperio2025</t>
-  </si>
-  <si>
-    <t>C:\Proyectos\-Auditoria\Control_pagos_anticipos_CyA\Data\Anticipos</t>
-  </si>
-  <si>
-    <t>AGRO BARGE SA</t>
-  </si>
-  <si>
-    <t>Santiago2025</t>
-  </si>
-  <si>
-    <t>AGROFRANCA SA</t>
-  </si>
-  <si>
-    <t>AGROSERVICIOS LA REVANCHA SA</t>
-  </si>
-  <si>
-    <t>Revancha2025</t>
-  </si>
-  <si>
-    <t>AGUAS &amp; PROCESOS SA</t>
-  </si>
-  <si>
-    <t>x4_6+aG3wwM6</t>
-  </si>
-  <si>
-    <t>BRACCO Y PORTA SA</t>
-  </si>
-  <si>
-    <t>OBracco63635</t>
-  </si>
-  <si>
-    <t>CDIMEX SA</t>
-  </si>
-  <si>
-    <t>Rafaela887</t>
-  </si>
-  <si>
-    <t>CONECTAR SRL</t>
-  </si>
-  <si>
-    <t>Crippa2025</t>
-  </si>
-  <si>
-    <t>COOP AGROPECUARIA "LA ARGENTINA" LTDA</t>
-  </si>
-  <si>
-    <t>Losbiava2025</t>
-  </si>
-  <si>
-    <t>DELLASANTA COMERCIAL SA</t>
-  </si>
-  <si>
-    <t>Oscar55OscarDE25</t>
-  </si>
-  <si>
-    <t>DOS LEGADOS SA</t>
-  </si>
-  <si>
-    <t>2025Gstuber</t>
-  </si>
-  <si>
-    <t>ECOWATT SAS</t>
-  </si>
-  <si>
-    <t>8x8bUlGe6T.7</t>
-  </si>
-  <si>
-    <t>ELECTRICIDAD PAGLIAROLI SA</t>
-  </si>
-  <si>
-    <t>Ginopa2025</t>
-  </si>
-  <si>
-    <t>ELECTROINSUMOS SA</t>
-  </si>
-  <si>
-    <t>Estudio2025GB</t>
-  </si>
-  <si>
-    <t>EQUIPOS AGROINDUSTRIALES SA</t>
-  </si>
-  <si>
-    <t>Guillermot37</t>
-  </si>
-  <si>
-    <t>ESCOBAR LITORAL SA</t>
-  </si>
-  <si>
-    <t>ESTAB. CANTAMALA SA</t>
-  </si>
-  <si>
-    <t>LGisbert397+</t>
+    <t>AGROTERRUM SA</t>
+  </si>
+  <si>
+    <t>ALIHEC SA</t>
+  </si>
+  <si>
+    <t>AMIPACK SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEAUTY GROUP </t>
+  </si>
+  <si>
+    <t>CA FERROCARRIL DEL ESTADO</t>
+  </si>
+  <si>
+    <t>DOSAR SA</t>
+  </si>
+  <si>
+    <t>EL ESPECTADOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR AUTOMORES SA</t>
+  </si>
+  <si>
+    <t>ESCOBAR SANTA FE SACIFI</t>
   </si>
   <si>
     <t>ESTUDIO RIVAROSSA Y ASOCIADOS</t>
   </si>
   <si>
-    <t>Emilia2025</t>
-  </si>
-  <si>
-    <t>ETMA SA</t>
-  </si>
-  <si>
-    <t>ACAGRA724p</t>
-  </si>
-  <si>
-    <t>GRUPO INBIO SA</t>
-  </si>
-  <si>
-    <t>FMarco2024</t>
-  </si>
-  <si>
-    <t>HERMANOS FUX SRL</t>
-  </si>
-  <si>
-    <t>Clarabu2025</t>
-  </si>
-  <si>
-    <t>ISIDORO S DELLASANTA y CÍA SAI y C</t>
-  </si>
-  <si>
-    <t>JIT INDUSTRIAL SA</t>
-  </si>
-  <si>
-    <t>Turc2025diego</t>
-  </si>
-  <si>
-    <t>LCGI SA</t>
-  </si>
-  <si>
-    <t>PabloB2025</t>
-  </si>
-  <si>
-    <t>LOS NARANJOS SA</t>
-  </si>
-  <si>
-    <t>w8BrI!6#S4r2</t>
-  </si>
-  <si>
-    <t>LZT AGRO SA</t>
-  </si>
-  <si>
-    <t>Lztagro2025</t>
-  </si>
-  <si>
-    <t>METALURGICA SAPINO SA</t>
-  </si>
-  <si>
-    <t>Roberto2025</t>
-  </si>
-  <si>
-    <t>METALÚRGICA SARMIENTO SRL</t>
-  </si>
-  <si>
-    <t>VictorSar2025</t>
-  </si>
-  <si>
-    <t>NATION MOTORS SA</t>
-  </si>
-  <si>
-    <t>Estudio2025</t>
-  </si>
-  <si>
-    <t>NATION SA</t>
-  </si>
-  <si>
-    <t>PLACE SA</t>
-  </si>
-  <si>
-    <t>ReneCh2023</t>
-  </si>
-  <si>
-    <t>ROBLE BIENES RAÍCES SA</t>
-  </si>
-  <si>
-    <t>EstudioR2025</t>
-  </si>
-  <si>
-    <t>SICEMI SCA</t>
+    <t>FECROL STAR SA</t>
+  </si>
+  <si>
+    <t>FIDEICOMISO LA COLONIA</t>
+  </si>
+  <si>
+    <t>MADERSA SRL</t>
+  </si>
+  <si>
+    <t>MARGARITA DISTRIBUIDORA SA</t>
+  </si>
+  <si>
+    <t>METALURGICA SARMIENTO SRL</t>
+  </si>
+  <si>
+    <t>SEVEL SRL</t>
   </si>
   <si>
     <t>SURGENTE MOLINOS SA</t>
   </si>
   <si>
-    <t>Mantovani2025</t>
-  </si>
-  <si>
     <t>TECHNO SA</t>
   </si>
   <si>
-    <t>Contarde2025</t>
-  </si>
-  <si>
     <t>TELCO INVERSORA SA</t>
   </si>
   <si>
-    <t>Carloswil25</t>
-  </si>
-  <si>
-    <t>TRANSPORTE LA 19 SA</t>
-  </si>
-  <si>
     <t>TREVISO SA</t>
   </si>
   <si>
-    <t>Jctrinca25</t>
-  </si>
-  <si>
-    <t>TRON SA</t>
-  </si>
-  <si>
-    <t>656ADiaz98</t>
+    <t>TRESAR SA</t>
   </si>
   <si>
     <t>WILSON SA</t>
   </si>
   <si>
     <t>WILTEL COMUNICACIONES SA</t>
-  </si>
-  <si>
-    <t>eSTUDIO2026</t>
   </si>
 </sst>
 </file>
@@ -321,9 +342,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -628,15 +652,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -661,24 +685,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>20295204681</v>
-      </c>
-      <c r="C2">
-        <v>30710314353</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>20062779137</v>
@@ -687,15 +703,15 @@
         <v>30711572410</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>20285770018</v>
@@ -704,32 +720,23 @@
         <v>30718810651</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>20329004385</v>
-      </c>
-      <c r="C5">
-        <v>33711615739</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>20248502704</v>
@@ -738,625 +745,668 @@
         <v>33602289619</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>20106361747</v>
-      </c>
-      <c r="C7">
-        <v>30518800775</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>20146535349</v>
-      </c>
-      <c r="C8">
-        <v>30711314489</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9">
-        <v>20301913053</v>
-      </c>
-      <c r="C9">
-        <v>30717751414</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>20278913520</v>
+        <v>20106361747</v>
       </c>
       <c r="C10">
-        <v>30605694191</v>
+        <v>30518800775</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11">
-        <v>20163036550</v>
-      </c>
-      <c r="C11">
-        <v>30708924896</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>20307649226</v>
+        <v>20146535349</v>
       </c>
       <c r="C12">
-        <v>30709634751</v>
+        <v>30711314489</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>20282211018</v>
+        <v>20301913053</v>
       </c>
       <c r="C13">
-        <v>30716468867</v>
+        <v>30717751414</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>20935609403</v>
+        <v>20278913520</v>
       </c>
       <c r="C14">
-        <v>30718725522</v>
+        <v>30605694191</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>23313646009</v>
+        <v>20163036550</v>
       </c>
       <c r="C15">
-        <v>33713343809</v>
+        <v>30708924896</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B16">
-        <v>20165740700</v>
+        <v>20307649226</v>
       </c>
       <c r="C16">
-        <v>30707213899</v>
+        <v>30709634751</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
-        <v>20295204681</v>
-      </c>
-      <c r="C17">
-        <v>30715417223</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B18">
-        <v>20173958863</v>
+        <v>20282211018</v>
       </c>
       <c r="C18">
-        <v>30711726183</v>
+        <v>30716468867</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
-        <v>20246845612</v>
-      </c>
-      <c r="C19">
-        <v>30715561227</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B20">
-        <v>27143384107</v>
+        <v>20935609403</v>
       </c>
       <c r="C20">
-        <v>30505523225</v>
+        <v>30718725522</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B21">
-        <v>20275663973</v>
+        <v>23313646009</v>
       </c>
       <c r="C21">
-        <v>30711642575</v>
+        <v>33713343809</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22">
-        <v>27340827061</v>
-      </c>
-      <c r="C22">
-        <v>30716870789</v>
-      </c>
-      <c r="D22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23">
-        <v>20163036550</v>
-      </c>
-      <c r="C23">
-        <v>30501721049</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>20161700860</v>
+        <v>20173958863</v>
       </c>
       <c r="C24">
-        <v>30717882306</v>
+        <v>30711726183</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25">
-        <v>20291157255</v>
-      </c>
-      <c r="C25">
-        <v>30715084011</v>
-      </c>
-      <c r="D25" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>20062610337</v>
+        <v>27143384107</v>
       </c>
       <c r="C26">
-        <v>30710847742</v>
+        <v>30505523225</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27">
-        <v>27146539705</v>
-      </c>
-      <c r="C27">
-        <v>33717433349</v>
-      </c>
-      <c r="D27" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28">
-        <v>20106363669</v>
-      </c>
-      <c r="C28">
-        <v>30714610291</v>
-      </c>
-      <c r="D28" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>23117583309</v>
+        <v>20275663973</v>
       </c>
       <c r="C29">
-        <v>30687011941</v>
+        <v>30711642575</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B30">
-        <v>27305018487</v>
+        <v>27340827061</v>
       </c>
       <c r="C30">
-        <v>30717391264</v>
+        <v>30716870789</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B31">
-        <v>23083223979</v>
+        <v>23162006789</v>
       </c>
       <c r="C31">
-        <v>30581697488</v>
+        <v>30708224290</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B32">
-        <v>20113062437</v>
+        <v>20163036550</v>
       </c>
       <c r="C32">
-        <v>30711603154</v>
+        <v>30501721049</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>27123041696</v>
+        <v>20161700860</v>
       </c>
       <c r="C33">
-        <v>30711669163</v>
+        <v>30717882306</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B34">
-        <v>23083223979</v>
+        <v>20291157255</v>
       </c>
       <c r="C34">
-        <v>30600549991</v>
+        <v>30715084011</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B35">
-        <v>20171140723</v>
+        <v>20062610337</v>
       </c>
       <c r="C35">
-        <v>30711767645</v>
+        <v>30710847742</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B36">
-        <v>20132420921</v>
+        <v>27146539705</v>
       </c>
       <c r="C36">
-        <v>30718347803</v>
+        <v>33717433349</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37">
-        <v>20169574597</v>
-      </c>
-      <c r="C37">
-        <v>30712789707</v>
-      </c>
-      <c r="D37" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38">
-        <v>20173958863</v>
-      </c>
-      <c r="C38">
-        <v>33711709199</v>
-      </c>
-      <c r="D38" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>23162006789</v>
+        <v>20106363669</v>
       </c>
       <c r="C39">
-        <v>30708873965</v>
+        <v>30714610291</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40">
-        <v>20131338245</v>
-      </c>
-      <c r="C40">
-        <v>30645578070</v>
-      </c>
-      <c r="D40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>20169574597</v>
+        <v>27305018487</v>
       </c>
       <c r="C41">
-        <v>30684389374</v>
+        <v>30717391264</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B42">
-        <v>20169574597</v>
+        <v>23083223979</v>
       </c>
       <c r="C42">
-        <v>30684386308</v>
+        <v>30581697488</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43">
+        <v>20113062437</v>
+      </c>
+      <c r="C43">
+        <v>30711603154</v>
+      </c>
+      <c r="D43" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44">
+        <v>23163038919</v>
+      </c>
+      <c r="C44">
+        <v>30715016334</v>
+      </c>
+      <c r="D44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45">
+        <v>20169323586</v>
+      </c>
+      <c r="C45">
+        <v>30716626977</v>
+      </c>
+      <c r="D45" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47">
+        <v>23083223979</v>
+      </c>
+      <c r="C47">
+        <v>30600549991</v>
+      </c>
+      <c r="D47" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51">
+        <v>20173958863</v>
+      </c>
+      <c r="C51">
+        <v>33711709199</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>85</v>
+      </c>
+      <c r="E53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54">
+        <v>20216000278</v>
+      </c>
+      <c r="C54">
+        <v>30645578070</v>
+      </c>
+      <c r="D54" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F54">
+    <sortCondition ref="A1:A54"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>